--- a/KBL-Business flow/target/Data/KBL datas2.xlsx
+++ b/KBL-Business flow/target/Data/KBL datas2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="14">
   <si>
     <t>1037</t>
   </si>
@@ -404,11 +404,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="2" width="13.576428571428572"/>
     <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="13.576428571428572"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="2" width="13.576428571428572"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -416,120 +417,143 @@
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" t="s" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" t="s" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" t="s" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" t="s" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" t="s" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" t="s" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" t="s" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" t="s" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" t="s" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" t="s" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" t="s" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" t="s" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" t="s" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
